--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run7/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run7/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,775 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.9615,0.0104,0.0068,0.0083</t>
-  </si>
-  <si>
-    <t>0.0341,0.0026,0.0004,0.9855</t>
-  </si>
-  <si>
-    <t>0.9808,0.0023,0.0009,0.0101</t>
-  </si>
-  <si>
-    <t>0.3563,0.0037,0.0009,0.7725</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0015,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9952,0.0019,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9956,0.0015,0.0002,0.0012</t>
-  </si>
-  <si>
-    <t>0.9939,0.0046,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9972,0.0003,0.0000,0.0014</t>
-  </si>
-  <si>
-    <t>0.9973,0.0007,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.8619,0.0061,0.1610,0.0029</t>
-  </si>
-  <si>
-    <t>0.1160,0.0047,0.9393,0.0008</t>
-  </si>
-  <si>
-    <t>0.0449,0.0080,0.9694,0.0006</t>
-  </si>
-  <si>
-    <t>0.0046,0.0025,0.9892,0.0026</t>
-  </si>
-  <si>
-    <t>0.9443,0.0052,0.0681,0.0012</t>
-  </si>
-  <si>
-    <t>0.0009,0.9966,0.0023,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.9945,0.0056,0.0011</t>
-  </si>
-  <si>
-    <t>0.0345,0.9625,0.0076,0.0012</t>
-  </si>
-  <si>
-    <t>0.0008,0.9970,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.0028,0.9944,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.7894,0.0170,0.1339,0.0461</t>
-  </si>
-  <si>
-    <t>0.4593,0.0062,0.1862,0.1532</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0364,0.0035,0.9628,0.0033</t>
-  </si>
-  <si>
-    <t>0.0325,0.0027,0.9760,0.0027</t>
-  </si>
-  <si>
-    <t>0.0032,0.0007,0.9910,0.0039</t>
-  </si>
-  <si>
-    <t>0.0444,0.0066,0.9591,0.0039</t>
-  </si>
-  <si>
-    <t>0.3426,0.7412,0.0028,0.0019</t>
-  </si>
-  <si>
-    <t>0.8303,0.1070,0.0454,0.0005</t>
-  </si>
-  <si>
-    <t>0.0013,0.0049,0.9926,0.0072</t>
-  </si>
-  <si>
-    <t>0.0072,0.9780,0.0099,0.0007</t>
-  </si>
-  <si>
-    <t>0.9587,0.0174,0.0205,0.0017</t>
-  </si>
-  <si>
-    <t>0.9213,0.0268,0.0456,0.0021</t>
-  </si>
-  <si>
-    <t>0.8680,0.1320,0.0015,0.0026</t>
-  </si>
-  <si>
-    <t>0.0059,0.9848,0.0229,0.0034</t>
-  </si>
-  <si>
-    <t>0.2189,0.3045,0.2017,0.0230</t>
-  </si>
-  <si>
-    <t>0.0117,0.0028,0.9584,0.0197</t>
-  </si>
-  <si>
-    <t>0.0368,0.0073,0.9763,0.0008</t>
-  </si>
-  <si>
-    <t>0.0392,0.0009,0.9575,0.0060</t>
-  </si>
-  <si>
-    <t>0.0496,0.0356,0.9642,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9989,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0028,0.9954,0.0010</t>
-  </si>
-  <si>
-    <t>0.0299,0.7242,0.0875,0.7178</t>
-  </si>
-  <si>
-    <t>0.0065,0.9807,0.0064,0.0074</t>
-  </si>
-  <si>
-    <t>0.0016,0.9918,0.0138,0.0031</t>
-  </si>
-  <si>
-    <t>0.0003,0.9983,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.0059,0.0241,0.9757,0.0075</t>
-  </si>
-  <si>
-    <t>0.0022,0.8522,0.9849,0.0011</t>
-  </si>
-  <si>
-    <t>0.0048,0.0064,0.9928,0.0017</t>
-  </si>
-  <si>
-    <t>0.0036,0.0023,0.9785,0.0310</t>
-  </si>
-  <si>
-    <t>0.0171,0.0054,0.9781,0.0030</t>
-  </si>
-  <si>
-    <t>0.0260,0.0154,0.9620,0.0040</t>
-  </si>
-  <si>
-    <t>0.9899,0.0073,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9878,0.0023,0.0059,0.0009</t>
-  </si>
-  <si>
-    <t>0.9658,0.0211,0.0069,0.0046</t>
-  </si>
-  <si>
-    <t>0.0013,0.0040,0.9941,0.0093</t>
-  </si>
-  <si>
-    <t>0.9940,0.0020,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9953,0.0019,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9783,0.0190,0.0031,0.0015</t>
-  </si>
-  <si>
-    <t>0.0047,0.7951,0.9526,0.0029</t>
-  </si>
-  <si>
-    <t>0.0362,0.0627,0.9425,0.0068</t>
-  </si>
-  <si>
-    <t>0.0091,0.0115,0.9533,0.0311</t>
-  </si>
-  <si>
-    <t>0.0007,0.9269,0.9816,0.0008</t>
-  </si>
-  <si>
-    <t>0.0027,0.0015,0.9914,0.0051</t>
-  </si>
-  <si>
-    <t>0.2605,0.8486,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.0023,0.9969,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.4467,0.0259,0.7040,0.0020</t>
-  </si>
-  <si>
-    <t>0.8928,0.0703,0.0489,0.0087</t>
-  </si>
-  <si>
-    <t>0.0068,0.0045,0.9921,0.0008</t>
-  </si>
-  <si>
-    <t>0.0041,0.6797,0.9537,0.0017</t>
-  </si>
-  <si>
-    <t>0.0006,0.9920,0.3702,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.9823,0.1176,0.0005</t>
-  </si>
-  <si>
-    <t>0.0043,0.9117,0.5364,0.0110</t>
-  </si>
-  <si>
-    <t>0.0302,0.0002,0.0011,0.9879</t>
-  </si>
-  <si>
-    <t>0.0010,0.0011,0.0002,0.9989</t>
-  </si>
-  <si>
-    <t>0.0045,0.0012,0.0003,0.9972</t>
-  </si>
-  <si>
-    <t>0.0184,0.0010,0.0001,0.9938</t>
-  </si>
-  <si>
-    <t>0.0106,0.0010,0.0041,0.9922</t>
-  </si>
-  <si>
-    <t>0.0173,0.0009,0.0002,0.9932</t>
-  </si>
-  <si>
-    <t>0.0019,0.9658,0.9193,0.0019</t>
-  </si>
-  <si>
-    <t>0.0019,0.3233,0.9846,0.0012</t>
-  </si>
-  <si>
-    <t>0.0056,0.9612,0.0823,0.0072</t>
-  </si>
-  <si>
-    <t>0.0035,0.8821,0.9363,0.0009</t>
-  </si>
-  <si>
-    <t>0.0027,0.9247,0.8133,0.0003</t>
-  </si>
-  <si>
-    <t>0.0060,0.7858,0.7001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9984,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9939,0.0066,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9918,0.0069,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9964,0.0014,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9964,0.0013,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9977,0.0008,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9682,0.0353,0.0021,0.0033</t>
-  </si>
-  <si>
-    <t>0.9921,0.0080,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9983,0.0007,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9963,0.0027,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9979,0.0004,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9976,0.0002,0.0000,0.0014</t>
-  </si>
-  <si>
-    <t>0.0135,0.0015,0.9840,0.0009</t>
-  </si>
-  <si>
-    <t>0.2518,0.0010,0.8149,0.0032</t>
-  </si>
-  <si>
-    <t>0.8609,0.0016,0.0879,0.0126</t>
-  </si>
-  <si>
-    <t>0.4620,0.0008,0.8033,0.0004</t>
-  </si>
-  <si>
-    <t>0.0020,0.9942,0.0006,0.0012</t>
-  </si>
-  <si>
-    <t>0.0032,0.9930,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.0109,0.9786,0.0203,0.0053</t>
-  </si>
-  <si>
-    <t>0.0902,0.9052,0.0206,0.0065</t>
-  </si>
-  <si>
-    <t>0.0045,0.9914,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.0017,0.9959,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.6178,0.3645,0.0352,0.0010</t>
-  </si>
-  <si>
-    <t>0.8567,0.0393,0.1227,0.0071</t>
-  </si>
-  <si>
-    <t>0.2306,0.0035,0.8912,0.0019</t>
-  </si>
-  <si>
-    <t>0.8613,0.0095,0.1398,0.0091</t>
-  </si>
-  <si>
-    <t>0.5944,0.0054,0.5612,0.0056</t>
-  </si>
-  <si>
-    <t>0.0443,0.1133,0.1617,0.8343</t>
-  </si>
-  <si>
-    <t>0.0003,0.9981,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.0031,0.9899,0.0121,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.9940,0.0080,0.0807</t>
-  </si>
-  <si>
-    <t>0.0013,0.9561,0.9581,0.0009</t>
-  </si>
-  <si>
-    <t>0.0059,0.9900,0.0021,0.0006</t>
-  </si>
-  <si>
-    <t>0.9572,0.0495,0.0045,0.0008</t>
-  </si>
-  <si>
-    <t>0.9243,0.0905,0.0121,0.0056</t>
-  </si>
-  <si>
-    <t>0.9982,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9957,0.0011,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9958,0.0010,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9605,0.0049,0.0365,0.0025</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9940,0.0008,0.0009,0.0013</t>
-  </si>
-  <si>
-    <t>0.9883,0.0020,0.0043,0.0017</t>
-  </si>
-  <si>
-    <t>0.9928,0.0008,0.0017,0.0011</t>
-  </si>
-  <si>
-    <t>0.0014,0.8549,0.9638,0.0011</t>
-  </si>
-  <si>
-    <t>0.0084,0.0861,0.9819,0.0003</t>
-  </si>
-  <si>
-    <t>0.0451,0.0019,0.9743,0.0002</t>
-  </si>
-  <si>
-    <t>0.0086,0.0041,0.9852,0.0022</t>
-  </si>
-  <si>
-    <t>0.9889,0.0012,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.7142,0.0215,0.2493,0.0422</t>
-  </si>
-  <si>
-    <t>0.1301,0.0024,0.9116,0.0065</t>
-  </si>
-  <si>
-    <t>0.8120,0.0304,0.1613,0.0067</t>
-  </si>
-  <si>
-    <t>0.1266,0.0011,0.0004,0.9644</t>
-  </si>
-  <si>
-    <t>0.0006,0.0005,0.0006,0.9991</t>
-  </si>
-  <si>
-    <t>0.0003,0.0084,0.0002,0.9991</t>
-  </si>
-  <si>
-    <t>0.0632,0.0001,0.0001,0.9891</t>
-  </si>
-  <si>
-    <t>0.0035,0.9704,0.0858,0.0010</t>
-  </si>
-  <si>
-    <t>0.9808,0.0039,0.0051,0.0036</t>
-  </si>
-  <si>
-    <t>0.2721,0.8128,0.0030,0.0030</t>
-  </si>
-  <si>
-    <t>0.9960,0.0004,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.7281,0.3283,0.0087,0.0051</t>
-  </si>
-  <si>
-    <t>0.9884,0.0004,0.0011,0.0040</t>
-  </si>
-  <si>
-    <t>0.0841,0.0053,0.0123,0.9428</t>
-  </si>
-  <si>
-    <t>0.9904,0.0014,0.0009,0.0021</t>
-  </si>
-  <si>
-    <t>0.0112,0.0064,0.7127,0.5663</t>
-  </si>
-  <si>
-    <t>0.1356,0.0037,0.0048,0.9098</t>
-  </si>
-  <si>
-    <t>0.9571,0.0020,0.0006,0.0406</t>
-  </si>
-  <si>
-    <t>0.4781,0.6338,0.0172,0.0045</t>
-  </si>
-  <si>
-    <t>0.9911,0.0036,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9922,0.0034,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.6132,0.5112,0.0055,0.0016</t>
-  </si>
-  <si>
-    <t>0.9334,0.0160,0.0718,0.0016</t>
-  </si>
-  <si>
-    <t>0.9897,0.0030,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.9825,0.0096,0.0037,0.0023</t>
-  </si>
-  <si>
-    <t>0.9976,0.0006,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9916,0.0029,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.9704,0.0001,0.0003,0.0463</t>
-  </si>
-  <si>
-    <t>0.9959,0.0004,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9920,0.0048,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9894,0.0016,0.0025,0.0019</t>
-  </si>
-  <si>
-    <t>0.9960,0.0003,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9467,0.0538,0.0007,0.0020</t>
-  </si>
-  <si>
-    <t>0.7053,0.3850,0.0029,0.0033</t>
-  </si>
-  <si>
-    <t>0.3404,0.7529,0.0036,0.0021</t>
-  </si>
-  <si>
-    <t>0.7532,0.1776,0.1669,0.0431</t>
-  </si>
-  <si>
-    <t>0.9955,0.0029,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9685,0.0139,0.0160,0.0026</t>
-  </si>
-  <si>
-    <t>0.9968,0.0005,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9825,0.0077,0.0017,0.0036</t>
-  </si>
-  <si>
-    <t>0.0006,0.0097,0.9986,0.0006</t>
-  </si>
-  <si>
-    <t>0.9887,0.0050,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.0021,0.0014,0.9971,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.0080,0.9903,0.0060</t>
-  </si>
-  <si>
-    <t>0.0027,0.0008,0.9883,0.0146</t>
-  </si>
-  <si>
-    <t>0.0285,0.0103,0.9654,0.0013</t>
-  </si>
-  <si>
-    <t>0.0042,0.0011,0.9954,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.0005,0.9978,0.0009</t>
-  </si>
-  <si>
-    <t>0.0027,0.0030,0.9950,0.0011</t>
-  </si>
-  <si>
-    <t>0.0898,0.0132,0.9122,0.0148</t>
-  </si>
-  <si>
-    <t>0.0352,0.0028,0.9616,0.0083</t>
-  </si>
-  <si>
-    <t>0.1153,0.0780,0.8406,0.0298</t>
-  </si>
-  <si>
-    <t>0.0855,0.0123,0.9276,0.0032</t>
-  </si>
-  <si>
-    <t>0.2394,0.2069,0.4760,0.0040</t>
-  </si>
-  <si>
-    <t>0.8786,0.0135,0.1489,0.0012</t>
-  </si>
-  <si>
-    <t>0.8316,0.0278,0.1727,0.0046</t>
-  </si>
-  <si>
-    <t>0.2055,0.0447,0.7650,0.0069</t>
-  </si>
-  <si>
-    <t>0.0971,0.9290,0.0015,0.0015</t>
-  </si>
-  <si>
-    <t>0.0378,0.9661,0.0026,0.0014</t>
-  </si>
-  <si>
-    <t>0.9093,0.1225,0.0018,0.0018</t>
-  </si>
-  <si>
-    <t>0.9902,0.0083,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.6034,0.5137,0.0093,0.0028</t>
-  </si>
-  <si>
-    <t>0.7663,0.1290,0.0831,0.0031</t>
-  </si>
-  <si>
-    <t>0.9758,0.0009,0.0162,0.0010</t>
-  </si>
-  <si>
-    <t>0.8617,0.0042,0.0771,0.0215</t>
-  </si>
-  <si>
-    <t>0.9667,0.0056,0.0236,0.0017</t>
-  </si>
-  <si>
-    <t>0.5054,0.0036,0.4125,0.0352</t>
-  </si>
-  <si>
-    <t>0.0323,0.0033,0.9578,0.0132</t>
-  </si>
-  <si>
-    <t>0.0153,0.0123,0.9586,0.0115</t>
-  </si>
-  <si>
-    <t>0.0157,0.0354,0.9746,0.0044</t>
-  </si>
-  <si>
-    <t>0.0877,0.0058,0.8358,0.0280</t>
-  </si>
-  <si>
-    <t>0.0095,0.0431,0.9665,0.0052</t>
-  </si>
-  <si>
-    <t>0.9877,0.0077,0.0010,0.0030</t>
-  </si>
-  <si>
-    <t>0.9933,0.0021,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9865,0.0069,0.0014,0.0032</t>
-  </si>
-  <si>
-    <t>0.9906,0.0053,0.0007,0.0017</t>
-  </si>
-  <si>
-    <t>0.9470,0.0454,0.0104,0.0062</t>
-  </si>
-  <si>
-    <t>0.9932,0.0043,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9928,0.0023,0.0006,0.0020</t>
-  </si>
-  <si>
-    <t>0.9952,0.0009,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.0029,0.0051,0.9947,0.0009</t>
-  </si>
-  <si>
-    <t>0.1339,0.4536,0.4933,0.1235</t>
-  </si>
-  <si>
-    <t>0.9118,0.0026,0.0595,0.0061</t>
-  </si>
-  <si>
-    <t>0.0169,0.0016,0.9868,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.0091,0.9951,0.0016</t>
-  </si>
-  <si>
-    <t>0.0464,0.0400,0.9170,0.0072</t>
-  </si>
-  <si>
-    <t>0.0016,0.0007,0.9935,0.0050</t>
-  </si>
-  <si>
-    <t>0.0108,0.0053,0.9809,0.0027</t>
-  </si>
-  <si>
-    <t>0.0010,0.0072,0.9918,0.0095</t>
-  </si>
-  <si>
-    <t>0.0123,0.0077,0.9094,0.0877</t>
-  </si>
-  <si>
-    <t>0.3471,0.0008,0.8506,0.0005</t>
-  </si>
-  <si>
-    <t>0.9652,0.0007,0.0157,0.0032</t>
-  </si>
-  <si>
-    <t>0.9130,0.0002,0.0569,0.0031</t>
-  </si>
-  <si>
-    <t>0.9235,0.0007,0.1716,0.0005</t>
-  </si>
-  <si>
-    <t>0.9955,0.0017,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9895,0.0070,0.0009,0.0015</t>
-  </si>
-  <si>
-    <t>0.9978,0.0014,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9898,0.0071,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9945,0.0058,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0017,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9920,0.0029,0.0010,0.0016</t>
-  </si>
-  <si>
-    <t>0.0112,0.0098,0.9766,0.0026</t>
-  </si>
-  <si>
-    <t>0.0088,0.2329,0.9729,0.0021</t>
-  </si>
-  <si>
-    <t>0.0264,0.0123,0.9401,0.0094</t>
-  </si>
-  <si>
-    <t>0.0172,0.0114,0.9743,0.0021</t>
-  </si>
-  <si>
-    <t>0.0432,0.0010,0.9442,0.0058</t>
-  </si>
-  <si>
-    <t>0.0106,0.0023,0.9601,0.0687</t>
-  </si>
-  <si>
-    <t>0.0094,0.0033,0.9640,0.0381</t>
-  </si>
-  <si>
-    <t>0.0494,0.0009,0.8822,0.0140</t>
-  </si>
-  <si>
-    <t>0.7335,0.0015,0.0040,0.2751</t>
-  </si>
-  <si>
-    <t>0.0082,0.0035,0.0012,0.9943</t>
-  </si>
-  <si>
-    <t>0.0144,0.0002,0.0006,0.9946</t>
-  </si>
-  <si>
-    <t>0.0019,0.0000,0.0002,0.9991</t>
-  </si>
-  <si>
-    <t>0.0011,0.0000,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.8813,0.0091,0.0047,0.0715</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.8455,0.0348,0.0123,0.0697</t>
+  </si>
+  <si>
+    <t>0.0100,0.0020,0.0014,0.9930</t>
+  </si>
+  <si>
+    <t>0.9653,0.0100,0.0012,0.0111</t>
+  </si>
+  <si>
+    <t>0.0550,0.0067,0.0034,0.9708</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9942,0.0008,0.0004,0.0031</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9955,0.0021,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9954,0.0024,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9944,0.0020,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9970,0.0007,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.7674,0.0028,0.4129,0.0009</t>
+  </si>
+  <si>
+    <t>0.0125,0.0102,0.9720,0.0079</t>
+  </si>
+  <si>
+    <t>0.3238,0.0012,0.8615,0.0001</t>
+  </si>
+  <si>
+    <t>0.0184,0.0065,0.9670,0.0116</t>
+  </si>
+  <si>
+    <t>0.9365,0.0034,0.0831,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.9992,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9959,0.0042,0.0021</t>
+  </si>
+  <si>
+    <t>0.0484,0.9627,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.0016,0.9949,0.0026,0.0007</t>
+  </si>
+  <si>
+    <t>0.0013,0.9965,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.8991,0.0040,0.0971,0.0059</t>
+  </si>
+  <si>
+    <t>0.2250,0.0140,0.7342,0.0421</t>
+  </si>
+  <si>
+    <t>0.0019,0.0003,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0087,0.0014,0.9878,0.0016</t>
+  </si>
+  <si>
+    <t>0.0111,0.0011,0.9904,0.0008</t>
+  </si>
+  <si>
+    <t>0.0047,0.0004,0.9934,0.0011</t>
+  </si>
+  <si>
+    <t>0.0111,0.0008,0.9882,0.0011</t>
+  </si>
+  <si>
+    <t>0.5001,0.6682,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.7782,0.0628,0.1939,0.0128</t>
+  </si>
+  <si>
+    <t>0.0005,0.0024,0.9948,0.0173</t>
+  </si>
+  <si>
+    <t>0.0052,0.9707,0.0719,0.0003</t>
+  </si>
+  <si>
+    <t>0.9859,0.0047,0.0041,0.0004</t>
+  </si>
+  <si>
+    <t>0.9882,0.0035,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.8900,0.1343,0.0052,0.0025</t>
+  </si>
+  <si>
+    <t>0.0233,0.9551,0.0287,0.0077</t>
+  </si>
+  <si>
+    <t>0.0441,0.6500,0.1693,0.0115</t>
+  </si>
+  <si>
+    <t>0.0008,0.0007,0.9952,0.0044</t>
+  </si>
+  <si>
+    <t>0.0326,0.0017,0.9635,0.0028</t>
+  </si>
+  <si>
+    <t>0.0096,0.0007,0.9657,0.0279</t>
+  </si>
+  <si>
+    <t>0.0172,0.0707,0.9700,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.9986,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0008,0.9952,0.0065</t>
+  </si>
+  <si>
+    <t>0.0212,0.1535,0.0031,0.9566</t>
+  </si>
+  <si>
+    <t>0.0041,0.9750,0.0108,0.0310</t>
+  </si>
+  <si>
+    <t>0.0020,0.9938,0.0054,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0147,0.0002</t>
+  </si>
+  <si>
+    <t>0.0086,0.0580,0.8514,0.0682</t>
+  </si>
+  <si>
+    <t>0.0032,0.0515,0.9865,0.0033</t>
+  </si>
+  <si>
+    <t>0.0094,0.0028,0.9834,0.0043</t>
+  </si>
+  <si>
+    <t>0.0787,0.0009,0.9637,0.0007</t>
+  </si>
+  <si>
+    <t>0.0035,0.0011,0.9938,0.0018</t>
+  </si>
+  <si>
+    <t>0.0024,0.0343,0.9843,0.0035</t>
+  </si>
+  <si>
+    <t>0.9879,0.0068,0.0015,0.0015</t>
+  </si>
+  <si>
+    <t>0.9856,0.0036,0.0069,0.0008</t>
+  </si>
+  <si>
+    <t>0.9812,0.0061,0.0074,0.0025</t>
+  </si>
+  <si>
+    <t>0.0027,0.0281,0.9840,0.0213</t>
+  </si>
+  <si>
+    <t>0.9850,0.0123,0.0034,0.0008</t>
+  </si>
+  <si>
+    <t>0.9941,0.0026,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9610,0.0217,0.0015,0.0090</t>
+  </si>
+  <si>
+    <t>0.0010,0.7827,0.9802,0.0004</t>
+  </si>
+  <si>
+    <t>0.0116,0.0058,0.9892,0.0009</t>
+  </si>
+  <si>
+    <t>0.0066,0.0774,0.9710,0.0054</t>
+  </si>
+  <si>
+    <t>0.0002,0.9405,0.9918,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.0007,0.9938,0.0054</t>
+  </si>
+  <si>
+    <t>0.0862,0.9341,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.0237,0.9832,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.7775,0.0051,0.4839,0.0007</t>
+  </si>
+  <si>
+    <t>0.8551,0.0980,0.0902,0.0049</t>
+  </si>
+  <si>
+    <t>0.0031,0.0059,0.9931,0.0014</t>
+  </si>
+  <si>
+    <t>0.0010,0.9105,0.9235,0.0005</t>
+  </si>
+  <si>
+    <t>0.0058,0.9123,0.8073,0.0013</t>
+  </si>
+  <si>
+    <t>0.0059,0.9524,0.4061,0.0015</t>
+  </si>
+  <si>
+    <t>0.0012,0.9675,0.8701,0.0012</t>
+  </si>
+  <si>
+    <t>0.0148,0.0002,0.0028,0.9896</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.0001,0.9994</t>
+  </si>
+  <si>
+    <t>0.0028,0.0002,0.0000,0.9988</t>
+  </si>
+  <si>
+    <t>0.0183,0.0023,0.0006,0.9909</t>
+  </si>
+  <si>
+    <t>0.0147,0.0004,0.0006,0.9946</t>
+  </si>
+  <si>
+    <t>0.0075,0.0014,0.0013,0.9940</t>
+  </si>
+  <si>
+    <t>0.0008,0.9560,0.9762,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.8311,0.9937,0.0008</t>
+  </si>
+  <si>
+    <t>0.0069,0.8470,0.5487,0.0041</t>
+  </si>
+  <si>
+    <t>0.0018,0.4070,0.9810,0.0019</t>
+  </si>
+  <si>
+    <t>0.0002,0.9804,0.9920,0.0001</t>
+  </si>
+  <si>
+    <t>0.0143,0.7923,0.3213,0.0006</t>
+  </si>
+  <si>
+    <t>0.9956,0.0016,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9931,0.0077,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9822,0.0256,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0028,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9920,0.0047,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9951,0.0028,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9858,0.0154,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9728,0.0150,0.0091,0.0018</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9969,0.0012,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9977,0.0008,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9967,0.0005,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.0059,0.0008,0.9873,0.0032</t>
+  </si>
+  <si>
+    <t>0.0416,0.0084,0.9577,0.0057</t>
+  </si>
+  <si>
+    <t>0.7777,0.0005,0.0366,0.0454</t>
+  </si>
+  <si>
+    <t>0.1875,0.0005,0.9174,0.0007</t>
+  </si>
+  <si>
+    <t>0.0036,0.9921,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.0028,0.9946,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.0173,0.9651,0.0020,0.0063</t>
+  </si>
+  <si>
+    <t>0.0310,0.9633,0.0062,0.0019</t>
+  </si>
+  <si>
+    <t>0.0045,0.9916,0.0040,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.9940,0.0055,0.0006</t>
+  </si>
+  <si>
+    <t>0.8104,0.1162,0.0949,0.0017</t>
+  </si>
+  <si>
+    <t>0.5386,0.0325,0.5363,0.0086</t>
+  </si>
+  <si>
+    <t>0.1009,0.0010,0.9439,0.0011</t>
+  </si>
+  <si>
+    <t>0.7275,0.0178,0.3179,0.0121</t>
+  </si>
+  <si>
+    <t>0.9088,0.0080,0.1131,0.0014</t>
+  </si>
+  <si>
+    <t>0.0228,0.2103,0.0759,0.8756</t>
+  </si>
+  <si>
+    <t>0.0043,0.9880,0.0055,0.0023</t>
+  </si>
+  <si>
+    <t>0.0006,0.9968,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.0008,0.9938,0.0050,0.0193</t>
+  </si>
+  <si>
+    <t>0.0007,0.9809,0.9224,0.0004</t>
+  </si>
+  <si>
+    <t>0.0055,0.9881,0.0077,0.0016</t>
+  </si>
+  <si>
+    <t>0.8715,0.1959,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.8700,0.1505,0.0074,0.0032</t>
+  </si>
+  <si>
+    <t>0.9965,0.0010,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9942,0.0019,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9956,0.0008,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9839,0.0021,0.0097,0.0011</t>
+  </si>
+  <si>
+    <t>0.9975,0.0002,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9937,0.0012,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9695,0.0189,0.0086,0.0040</t>
+  </si>
+  <si>
+    <t>0.9867,0.0030,0.0040,0.0013</t>
+  </si>
+  <si>
+    <t>0.0030,0.8885,0.9033,0.0013</t>
+  </si>
+  <si>
+    <t>0.0226,0.4446,0.8824,0.0006</t>
+  </si>
+  <si>
+    <t>0.0127,0.0492,0.9745,0.0025</t>
+  </si>
+  <si>
+    <t>0.0175,0.2135,0.9534,0.0027</t>
+  </si>
+  <si>
+    <t>0.9629,0.0022,0.0234,0.0009</t>
+  </si>
+  <si>
+    <t>0.7053,0.0090,0.2756,0.0307</t>
+  </si>
+  <si>
+    <t>0.5594,0.0021,0.6583,0.0014</t>
+  </si>
+  <si>
+    <t>0.7943,0.0311,0.1788,0.0076</t>
+  </si>
+  <si>
+    <t>0.0418,0.0005,0.0001,0.9902</t>
+  </si>
+  <si>
+    <t>0.0006,0.0011,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.0021,0.0095,0.0006,0.9968</t>
+  </si>
+  <si>
+    <t>0.0487,0.0006,0.0011,0.9841</t>
+  </si>
+  <si>
+    <t>0.0006,0.9741,0.6249,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0022,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0972,0.9164,0.0054,0.0028</t>
+  </si>
+  <si>
+    <t>0.9922,0.0011,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.7254,0.3166,0.0233,0.0021</t>
+  </si>
+  <si>
+    <t>0.9909,0.0017,0.0026,0.0011</t>
+  </si>
+  <si>
+    <t>0.5146,0.0097,0.0121,0.4564</t>
+  </si>
+  <si>
+    <t>0.9924,0.0013,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.0065,0.0165,0.8395,0.3553</t>
+  </si>
+  <si>
+    <t>0.6383,0.0028,0.0146,0.2888</t>
+  </si>
+  <si>
+    <t>0.9022,0.0006,0.0034,0.0893</t>
+  </si>
+  <si>
+    <t>0.7578,0.2542,0.0348,0.0069</t>
+  </si>
+  <si>
+    <t>0.9926,0.0034,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9717,0.0134,0.0105,0.0011</t>
+  </si>
+  <si>
+    <t>0.3684,0.7075,0.0227,0.0018</t>
+  </si>
+  <si>
+    <t>0.9544,0.0037,0.0566,0.0011</t>
+  </si>
+  <si>
+    <t>0.9843,0.0022,0.0082,0.0004</t>
+  </si>
+  <si>
+    <t>0.9956,0.0018,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9969,0.0006,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9920,0.0031,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9939,0.0002,0.0005,0.0025</t>
+  </si>
+  <si>
+    <t>0.9878,0.0023,0.0025,0.0034</t>
+  </si>
+  <si>
+    <t>0.9930,0.0026,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.9961,0.0005,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9896,0.0007,0.0004,0.0075</t>
+  </si>
+  <si>
+    <t>0.7536,0.3035,0.0064,0.0035</t>
+  </si>
+  <si>
+    <t>0.6183,0.5253,0.0050,0.0014</t>
+  </si>
+  <si>
+    <t>0.4325,0.6780,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.2772,0.6178,0.5140,0.0309</t>
+  </si>
+  <si>
+    <t>0.9947,0.0040,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9910,0.0017,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.9928,0.0034,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9241,0.1127,0.0054,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0018,0.9992,0.0022</t>
+  </si>
+  <si>
+    <t>0.9703,0.0097,0.0136,0.0006</t>
+  </si>
+  <si>
+    <t>0.0077,0.0012,0.9945,0.0001</t>
+  </si>
+  <si>
+    <t>0.0040,0.0029,0.9918,0.0016</t>
+  </si>
+  <si>
+    <t>0.0091,0.0011,0.9864,0.0073</t>
+  </si>
+  <si>
+    <t>0.0964,0.0143,0.9017,0.0007</t>
+  </si>
+  <si>
+    <t>0.0059,0.0075,0.9930,0.0004</t>
+  </si>
+  <si>
+    <t>0.0029,0.0005,0.9950,0.0017</t>
+  </si>
+  <si>
+    <t>0.0008,0.0014,0.9979,0.0006</t>
+  </si>
+  <si>
+    <t>0.1672,0.0355,0.8154,0.0193</t>
+  </si>
+  <si>
+    <t>0.4529,0.0037,0.7338,0.0010</t>
+  </si>
+  <si>
+    <t>0.2354,0.0270,0.8051,0.0173</t>
+  </si>
+  <si>
+    <t>0.2834,0.0569,0.7184,0.0042</t>
+  </si>
+  <si>
+    <t>0.3506,0.2113,0.4160,0.0042</t>
+  </si>
+  <si>
+    <t>0.2025,0.0346,0.7907,0.0136</t>
+  </si>
+  <si>
+    <t>0.9615,0.0046,0.0348,0.0013</t>
+  </si>
+  <si>
+    <t>0.3534,0.0251,0.7598,0.0065</t>
+  </si>
+  <si>
+    <t>0.5745,0.6083,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.2586,0.8478,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9177,0.1431,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9741,0.0213,0.0049,0.0018</t>
+  </si>
+  <si>
+    <t>0.8899,0.1607,0.0060,0.0030</t>
+  </si>
+  <si>
+    <t>0.8652,0.0528,0.0899,0.0021</t>
+  </si>
+  <si>
+    <t>0.9832,0.0005,0.0121,0.0005</t>
+  </si>
+  <si>
+    <t>0.9368,0.0082,0.0210,0.0105</t>
+  </si>
+  <si>
+    <t>0.8482,0.0018,0.1819,0.0043</t>
+  </si>
+  <si>
+    <t>0.9484,0.0043,0.0362,0.0016</t>
+  </si>
+  <si>
+    <t>0.0043,0.0010,0.9850,0.0117</t>
+  </si>
+  <si>
+    <t>0.0078,0.0042,0.9791,0.0114</t>
+  </si>
+  <si>
+    <t>0.0336,0.0265,0.9526,0.0114</t>
+  </si>
+  <si>
+    <t>0.0395,0.0017,0.9532,0.0063</t>
+  </si>
+  <si>
+    <t>0.0033,0.0423,0.9833,0.0016</t>
+  </si>
+  <si>
+    <t>0.9978,0.0006,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9948,0.0018,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9742,0.0233,0.0040,0.0040</t>
+  </si>
+  <si>
+    <t>0.9901,0.0066,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9819,0.0107,0.0045,0.0014</t>
+  </si>
+  <si>
+    <t>0.9961,0.0008,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9944,0.0006,0.0004,0.0024</t>
+  </si>
+  <si>
+    <t>0.9929,0.0009,0.0010,0.0030</t>
+  </si>
+  <si>
+    <t>0.0023,0.0100,0.9902,0.0033</t>
+  </si>
+  <si>
+    <t>0.0604,0.0458,0.9264,0.0084</t>
+  </si>
+  <si>
+    <t>0.9306,0.0031,0.0522,0.0039</t>
+  </si>
+  <si>
+    <t>0.0167,0.0026,0.9797,0.0031</t>
+  </si>
+  <si>
+    <t>0.0011,0.1688,0.9936,0.0015</t>
+  </si>
+  <si>
+    <t>0.0481,0.1361,0.7946,0.0089</t>
+  </si>
+  <si>
+    <t>0.0002,0.0020,0.9964,0.0178</t>
+  </si>
+  <si>
+    <t>0.0078,0.0112,0.9726,0.0068</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9980,0.0008</t>
+  </si>
+  <si>
+    <t>0.0055,0.0069,0.9124,0.1455</t>
+  </si>
+  <si>
+    <t>0.4126,0.0006,0.8258,0.0003</t>
+  </si>
+  <si>
+    <t>0.9647,0.0006,0.0181,0.0031</t>
+  </si>
+  <si>
+    <t>0.8932,0.0005,0.2406,0.0003</t>
+  </si>
+  <si>
+    <t>0.9518,0.0060,0.0439,0.0010</t>
+  </si>
+  <si>
+    <t>0.9870,0.0112,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.9910,0.0100,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9939,0.0038,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9803,0.0146,0.0033,0.0013</t>
+  </si>
+  <si>
+    <t>0.9937,0.0011,0.0022,0.0006</t>
+  </si>
+  <si>
+    <t>0.9972,0.0023,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0024,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0018,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0605,0.2539,0.5727,0.0378</t>
+  </si>
+  <si>
+    <t>0.0053,0.2101,0.9779,0.0015</t>
+  </si>
+  <si>
+    <t>0.0117,0.0095,0.9708,0.0042</t>
+  </si>
+  <si>
+    <t>0.0392,0.0527,0.9284,0.0020</t>
+  </si>
+  <si>
+    <t>0.0180,0.0025,0.9731,0.0044</t>
+  </si>
+  <si>
+    <t>0.0082,0.0008,0.9848,0.0107</t>
+  </si>
+  <si>
+    <t>0.0307,0.0057,0.9522,0.0180</t>
+  </si>
+  <si>
+    <t>0.0025,0.0001,0.9800,0.0146</t>
+  </si>
+  <si>
+    <t>0.5012,0.0064,0.0167,0.4466</t>
+  </si>
+  <si>
+    <t>0.0369,0.0127,0.0079,0.9735</t>
+  </si>
+  <si>
+    <t>0.0223,0.0004,0.0001,0.9937</t>
+  </si>
+  <si>
+    <t>0.0027,0.0001,0.0007,0.9980</t>
+  </si>
+  <si>
+    <t>0.0018,0.0004,0.0013,0.9980</t>
+  </si>
+  <si>
+    <t>0.9684,0.0082,0.0028,0.0087</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1976,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1990,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2004,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2018,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2032,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2046,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2060,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2088,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2102,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2116,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2130,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2144,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2158,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2172,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2228,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2270,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2298,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2312,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2326,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2340,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2354,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2382,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2396,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2410,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2424,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2438,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2452,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,10 +2480,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2494,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2508,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2522,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2536,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2564,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2634,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,10 +2648,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2662,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2676,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2690,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2704,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2718,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2732,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2746,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2760,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2774,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2788,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2802,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2816,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2830,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2844,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2872,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2928,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2942,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2956,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,10 +2970,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2984,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2998,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3012,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3026,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3040,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3054,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3068,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3082,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3096,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3152,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3180,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3194,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3208,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3222,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3236,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3250,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3264,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3278,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3292,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3306,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3320,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3334,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3348,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3362,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3376,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3390,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3404,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3418,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3432,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3544,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3572,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3586,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3614,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3656,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3698,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3712,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3810,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3824,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3838,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3852,7 +3855,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3866,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3880,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D142" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3936,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3950,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,10 +4006,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4034,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4062,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4104,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,10 +4118,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4146,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4174,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4188,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4202,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4286,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4300,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4356,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4384,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4440,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4454,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4468,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4496,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4510,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4524,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4538,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4552,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4566,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4580,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4594,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4622,7 +4625,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4636,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4678,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4692,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4804,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4818,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4832,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4846,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4860,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4874,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4888,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4902,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4916,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4930,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5014,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5028,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5070,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5084,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5098,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5112,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5126,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5140,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5154,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5168,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5182,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5196,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5210,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5336,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5350,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5364,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5378,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5392,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5406,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5434,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5448,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5518,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
